--- a/AAII_Financials/Yearly/BAESY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BAESY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,37 +656,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="F7" s="2" t="s">
         <v>3</v>
       </c>
@@ -705,17 +705,20 @@
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>26372700</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
+        <v>29426800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>27106100</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
@@ -735,17 +738,20 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>8763600</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
+        <v>10003200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>9007300</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
@@ -765,17 +771,20 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>17609100</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
+        <v>19423600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>18098800</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
@@ -795,9 +804,12 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,16 +822,17 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>342400</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
+        <v>349400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>351900</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,17 +885,20 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-103000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+        <v>-54800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-105800</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -899,17 +918,20 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>947800</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
+        <v>997100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>974200</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>3</v>
@@ -929,9 +951,12 @@
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,16 +966,17 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>23415100</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>3</v>
+        <v>26145900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>24066200</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>3</v>
@@ -970,17 +996,20 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2957600</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
+        <v>3280800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3039800</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
@@ -1000,9 +1029,12 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,16 +1047,17 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-156300</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
+        <v>117300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-160700</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -1044,17 +1077,20 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3753700</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
+        <v>4405200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3860600</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -1074,17 +1110,20 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>333700</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
+        <v>432300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>343000</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -1104,17 +1143,20 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2467600</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>3</v>
+        <v>2965900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2536200</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>3</v>
@@ -1134,17 +1176,20 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>390800</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+        <v>492200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>401700</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1164,9 +1209,12 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,17 +1242,20 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2076800</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>3</v>
+        <v>2473700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2134500</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
@@ -1224,17 +1275,20 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1973800</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>3</v>
+        <v>2367900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2028700</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
@@ -1254,9 +1308,12 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1311,12 +1371,15 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,17 +1440,20 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>156300</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
+        <v>-117300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>160700</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -1404,17 +1473,20 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1973800</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>3</v>
+        <v>2367900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2028700</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
@@ -1434,9 +1506,12 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,17 +1539,20 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1973800</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>3</v>
+        <v>2367900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2028700</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>3</v>
@@ -1494,23 +1572,26 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="F38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1529,9 +1610,12 @@
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,16 +1643,17 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2025900</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>3</v>
+        <v>2393400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2082200</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>3</v>
@@ -1587,17 +1673,20 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2141300</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
+        <v>3053900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2200800</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
@@ -1617,17 +1706,20 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7183100</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+        <v>6900800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>7382800</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -1647,17 +1739,20 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1210800</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
+        <v>1474000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1244500</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1677,17 +1772,20 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>631500</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+        <v>1189700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>649000</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -1707,17 +1805,20 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>13192500</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>3</v>
+        <v>15011800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>13559400</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
@@ -1737,17 +1838,20 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1208300</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
+        <v>1267400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1241900</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -1767,17 +1871,20 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5859400</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
+        <v>6379300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6022300</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1797,17 +1904,20 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>15686100</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
+        <v>15427400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>16122400</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
@@ -1827,9 +1937,12 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,17 +2003,20 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3085400</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+        <v>2798800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3171200</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -1917,9 +2036,12 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,17 +2069,20 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>39031800</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>3</v>
+        <v>40884800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>40117200</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>3</v>
@@ -1977,9 +2102,12 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,16 +2135,17 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2357100</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
+        <v>3060200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2422700</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -2035,17 +2165,20 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>364700</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+        <v>1053200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>374900</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -2065,17 +2198,20 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9493100</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
+        <v>9839900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>9757100</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
@@ -2095,17 +2231,20 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>12214900</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>3</v>
+        <v>13953400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12554600</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>3</v>
@@ -2125,17 +2264,20 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8143300</v>
+        <v>7274400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>8369800</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2155,17 +2297,20 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4530700</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
+        <v>5984000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4656700</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2185,9 +2330,12 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,17 +2429,20 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>25118400</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>3</v>
+        <v>27421000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>25816900</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
@@ -2305,9 +2462,12 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,17 +2609,20 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>9588600</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
+        <v>9718800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>9855200</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -2469,9 +2642,12 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,17 +2741,20 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13913300</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>3</v>
+        <v>13463800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>14300200</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
@@ -2589,9 +2774,12 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,23 +2807,26 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="F80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2654,17 +2845,20 @@
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1973800</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>3</v>
+        <v>2367900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2028700</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>3</v>
@@ -2684,9 +2878,12 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,16 +2896,17 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>951500</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+        <v>1003500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>978000</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -2728,9 +2926,12 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,17 +3091,20 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3522100</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
+        <v>4794400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3620000</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
@@ -2908,9 +3124,12 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,16 +3142,17 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-743100</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+        <v>-1053200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-763800</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
@@ -2952,9 +3172,12 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,17 +3238,20 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-523500</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+        <v>-689800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-538100</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -3042,9 +3271,12 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,16 +3289,17 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-995000</v>
+        <v>-1092800</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-1022600</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3086,9 +3319,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,17 +3418,20 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2894300</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
+        <v>-2789900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2974800</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
@@ -3206,17 +3451,20 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>131500</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+        <v>-90500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>135200</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3236,17 +3484,20 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>235700</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
+        <v>1224100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>242300</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>3</v>
@@ -3266,7 +3517,10 @@
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BAESY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BAESY_YR_FIN.xlsx
@@ -715,10 +715,10 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>29426800</v>
+        <v>29530800</v>
       </c>
       <c r="E8" s="3">
-        <v>27106100</v>
+        <v>27201900</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
@@ -748,10 +748,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>10003200</v>
+        <v>10038500</v>
       </c>
       <c r="E9" s="3">
-        <v>9007300</v>
+        <v>9039200</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
@@ -781,10 +781,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>19423600</v>
+        <v>19492300</v>
       </c>
       <c r="E10" s="3">
-        <v>18098800</v>
+        <v>18162800</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
@@ -829,10 +829,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>349400</v>
+        <v>350600</v>
       </c>
       <c r="E12" s="3">
-        <v>351900</v>
+        <v>353200</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
@@ -895,10 +895,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-54800</v>
+        <v>-55000</v>
       </c>
       <c r="E14" s="3">
-        <v>-105800</v>
+        <v>-106200</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -928,10 +928,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>997100</v>
+        <v>1000700</v>
       </c>
       <c r="E15" s="3">
-        <v>974200</v>
+        <v>977600</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>3</v>
@@ -973,10 +973,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>26145900</v>
+        <v>26238400</v>
       </c>
       <c r="E17" s="3">
-        <v>24066200</v>
+        <v>24151400</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>3</v>
@@ -1006,10 +1006,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3280800</v>
+        <v>3292400</v>
       </c>
       <c r="E18" s="3">
-        <v>3039800</v>
+        <v>3050600</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
@@ -1054,10 +1054,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>117300</v>
+        <v>117700</v>
       </c>
       <c r="E20" s="3">
-        <v>-160700</v>
+        <v>-161200</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -1087,10 +1087,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4405200</v>
+        <v>4412800</v>
       </c>
       <c r="E21" s="3">
-        <v>3860600</v>
+        <v>3866500</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -1120,10 +1120,10 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>432300</v>
+        <v>433800</v>
       </c>
       <c r="E22" s="3">
-        <v>343000</v>
+        <v>344200</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -1153,10 +1153,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2965900</v>
+        <v>2976400</v>
       </c>
       <c r="E23" s="3">
-        <v>2536200</v>
+        <v>2545100</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>3</v>
@@ -1186,10 +1186,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>492200</v>
+        <v>493900</v>
       </c>
       <c r="E24" s="3">
-        <v>401700</v>
+        <v>403100</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1252,10 +1252,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2473700</v>
+        <v>2482400</v>
       </c>
       <c r="E26" s="3">
-        <v>2134500</v>
+        <v>2142100</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
@@ -1285,10 +1285,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2367900</v>
+        <v>2376200</v>
       </c>
       <c r="E27" s="3">
-        <v>2028700</v>
+        <v>2035900</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
@@ -1450,10 +1450,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-117300</v>
+        <v>-117700</v>
       </c>
       <c r="E32" s="3">
-        <v>160700</v>
+        <v>161200</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -1483,10 +1483,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2367900</v>
+        <v>2376200</v>
       </c>
       <c r="E33" s="3">
-        <v>2028700</v>
+        <v>2035900</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
@@ -1549,10 +1549,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2367900</v>
+        <v>2376200</v>
       </c>
       <c r="E35" s="3">
-        <v>2028700</v>
+        <v>2035900</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>3</v>
@@ -1650,10 +1650,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2393400</v>
+        <v>2401800</v>
       </c>
       <c r="E41" s="3">
-        <v>2082200</v>
+        <v>2089600</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>3</v>
@@ -1683,10 +1683,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3053900</v>
+        <v>3064700</v>
       </c>
       <c r="E42" s="3">
-        <v>2200800</v>
+        <v>2208600</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
@@ -1716,10 +1716,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6900800</v>
+        <v>6925200</v>
       </c>
       <c r="E43" s="3">
-        <v>7382800</v>
+        <v>7408900</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -1749,10 +1749,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1474000</v>
+        <v>1479200</v>
       </c>
       <c r="E44" s="3">
-        <v>1244500</v>
+        <v>1248900</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1782,10 +1782,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1189700</v>
+        <v>1193900</v>
       </c>
       <c r="E45" s="3">
-        <v>649000</v>
+        <v>651300</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -1815,10 +1815,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>15011800</v>
+        <v>15064800</v>
       </c>
       <c r="E46" s="3">
-        <v>13559400</v>
+        <v>13607400</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
@@ -1848,10 +1848,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1267400</v>
+        <v>1271900</v>
       </c>
       <c r="E47" s="3">
-        <v>1241900</v>
+        <v>1246300</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -1881,10 +1881,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6379300</v>
+        <v>6401900</v>
       </c>
       <c r="E48" s="3">
-        <v>6022300</v>
+        <v>6043600</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1914,10 +1914,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>15427400</v>
+        <v>15482000</v>
       </c>
       <c r="E49" s="3">
-        <v>16122400</v>
+        <v>16179400</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
@@ -2013,10 +2013,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2798800</v>
+        <v>2808700</v>
       </c>
       <c r="E52" s="3">
-        <v>3171200</v>
+        <v>3182400</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -2079,10 +2079,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>40884800</v>
+        <v>41029400</v>
       </c>
       <c r="E54" s="3">
-        <v>40117200</v>
+        <v>40259100</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>3</v>
@@ -2142,10 +2142,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3060200</v>
+        <v>3071100</v>
       </c>
       <c r="E57" s="3">
-        <v>2422700</v>
+        <v>2431300</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -2175,10 +2175,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1053200</v>
+        <v>1057000</v>
       </c>
       <c r="E58" s="3">
-        <v>374900</v>
+        <v>376200</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -2208,10 +2208,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9839900</v>
+        <v>9874800</v>
       </c>
       <c r="E59" s="3">
-        <v>9757100</v>
+        <v>9791600</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
@@ -2241,10 +2241,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>13953400</v>
+        <v>14002800</v>
       </c>
       <c r="E60" s="3">
-        <v>12554600</v>
+        <v>12599000</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>3</v>
@@ -2274,10 +2274,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7274400</v>
+        <v>7300200</v>
       </c>
       <c r="E61" s="3">
-        <v>8369800</v>
+        <v>8399400</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2307,10 +2307,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5984000</v>
+        <v>6005200</v>
       </c>
       <c r="E62" s="3">
-        <v>4656700</v>
+        <v>4673100</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2439,10 +2439,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>27421000</v>
+        <v>27518000</v>
       </c>
       <c r="E66" s="3">
-        <v>25816900</v>
+        <v>25908300</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
@@ -2619,10 +2619,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>9718800</v>
+        <v>9753200</v>
       </c>
       <c r="E72" s="3">
-        <v>9855200</v>
+        <v>9890100</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -2751,10 +2751,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13463800</v>
+        <v>13511400</v>
       </c>
       <c r="E76" s="3">
-        <v>14300200</v>
+        <v>14350800</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
@@ -2855,10 +2855,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2367900</v>
+        <v>2376200</v>
       </c>
       <c r="E81" s="3">
-        <v>2028700</v>
+        <v>2035900</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>3</v>
@@ -2903,10 +2903,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1003500</v>
+        <v>1007100</v>
       </c>
       <c r="E83" s="3">
-        <v>978000</v>
+        <v>981500</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -3101,10 +3101,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4794400</v>
+        <v>4811300</v>
       </c>
       <c r="E89" s="3">
-        <v>3620000</v>
+        <v>3632800</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
@@ -3149,10 +3149,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1053200</v>
+        <v>-1057000</v>
       </c>
       <c r="E91" s="3">
-        <v>-763800</v>
+        <v>-766500</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
@@ -3248,10 +3248,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-689800</v>
+        <v>-692300</v>
       </c>
       <c r="E94" s="3">
-        <v>-538100</v>
+        <v>-540000</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -3296,10 +3296,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1092800</v>
+        <v>-1096600</v>
       </c>
       <c r="E96" s="3">
-        <v>-1022600</v>
+        <v>-1026200</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3428,10 +3428,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2789900</v>
+        <v>-2799800</v>
       </c>
       <c r="E100" s="3">
-        <v>-2974800</v>
+        <v>-2985300</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
@@ -3461,10 +3461,10 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-90500</v>
+        <v>-90900</v>
       </c>
       <c r="E101" s="3">
-        <v>135200</v>
+        <v>135600</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3494,10 +3494,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1224100</v>
+        <v>1228400</v>
       </c>
       <c r="E102" s="3">
-        <v>242300</v>
+        <v>243100</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/BAESY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BAESY_YR_FIN.xlsx
@@ -715,10 +715,10 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>29530800</v>
+        <v>30283000</v>
       </c>
       <c r="E8" s="3">
-        <v>27201900</v>
+        <v>27894700</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
@@ -748,10 +748,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>10038500</v>
+        <v>10294200</v>
       </c>
       <c r="E9" s="3">
-        <v>9039200</v>
+        <v>9269400</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
@@ -781,10 +781,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>19492300</v>
+        <v>19988700</v>
       </c>
       <c r="E10" s="3">
-        <v>18162800</v>
+        <v>18625400</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
@@ -829,10 +829,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>350600</v>
+        <v>359500</v>
       </c>
       <c r="E12" s="3">
-        <v>353200</v>
+        <v>362200</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
@@ -895,10 +895,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-55000</v>
+        <v>-56400</v>
       </c>
       <c r="E14" s="3">
-        <v>-106200</v>
+        <v>-108900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -928,10 +928,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1000700</v>
+        <v>1026100</v>
       </c>
       <c r="E15" s="3">
-        <v>977600</v>
+        <v>1002500</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>3</v>
@@ -973,10 +973,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>26238400</v>
+        <v>26906700</v>
       </c>
       <c r="E17" s="3">
-        <v>24151400</v>
+        <v>24766500</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>3</v>
@@ -1006,10 +1006,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3292400</v>
+        <v>3376300</v>
       </c>
       <c r="E18" s="3">
-        <v>3050600</v>
+        <v>3128300</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
@@ -1054,10 +1054,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>117700</v>
+        <v>120700</v>
       </c>
       <c r="E20" s="3">
-        <v>-161200</v>
+        <v>-165300</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -1087,10 +1087,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4412800</v>
+        <v>4529800</v>
       </c>
       <c r="E21" s="3">
-        <v>3866500</v>
+        <v>3969500</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -1120,10 +1120,10 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>433800</v>
+        <v>444800</v>
       </c>
       <c r="E22" s="3">
-        <v>344200</v>
+        <v>353000</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -1153,10 +1153,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2976400</v>
+        <v>3052200</v>
       </c>
       <c r="E23" s="3">
-        <v>2545100</v>
+        <v>2610000</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>3</v>
@@ -1186,10 +1186,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>493900</v>
+        <v>506500</v>
       </c>
       <c r="E24" s="3">
-        <v>403100</v>
+        <v>413300</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1252,10 +1252,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2482400</v>
+        <v>2545700</v>
       </c>
       <c r="E26" s="3">
-        <v>2142100</v>
+        <v>2196600</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
@@ -1285,10 +1285,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2376200</v>
+        <v>2436800</v>
       </c>
       <c r="E27" s="3">
-        <v>2035900</v>
+        <v>2087700</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
@@ -1450,10 +1450,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-117700</v>
+        <v>-120700</v>
       </c>
       <c r="E32" s="3">
-        <v>161200</v>
+        <v>165300</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -1483,10 +1483,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2376200</v>
+        <v>2436800</v>
       </c>
       <c r="E33" s="3">
-        <v>2035900</v>
+        <v>2087700</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
@@ -1549,10 +1549,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2376200</v>
+        <v>2436800</v>
       </c>
       <c r="E35" s="3">
-        <v>2035900</v>
+        <v>2087700</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>3</v>
@@ -1650,10 +1650,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2401800</v>
+        <v>2463000</v>
       </c>
       <c r="E41" s="3">
-        <v>2089600</v>
+        <v>2142800</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>3</v>
@@ -1683,10 +1683,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3064700</v>
+        <v>3142700</v>
       </c>
       <c r="E42" s="3">
-        <v>2208600</v>
+        <v>2264900</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
@@ -1716,10 +1716,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6925200</v>
+        <v>7101600</v>
       </c>
       <c r="E43" s="3">
-        <v>7408900</v>
+        <v>7597600</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -1749,10 +1749,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1479200</v>
+        <v>1516900</v>
       </c>
       <c r="E44" s="3">
-        <v>1248900</v>
+        <v>1280700</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1782,10 +1782,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1193900</v>
+        <v>1224300</v>
       </c>
       <c r="E45" s="3">
-        <v>651300</v>
+        <v>667900</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -1815,10 +1815,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>15064800</v>
+        <v>15448500</v>
       </c>
       <c r="E46" s="3">
-        <v>13607400</v>
+        <v>13953900</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
@@ -1848,10 +1848,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1271900</v>
+        <v>1304300</v>
       </c>
       <c r="E47" s="3">
-        <v>1246300</v>
+        <v>1278100</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -1881,10 +1881,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6401900</v>
+        <v>6564900</v>
       </c>
       <c r="E48" s="3">
-        <v>6043600</v>
+        <v>6197500</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1914,10 +1914,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>15482000</v>
+        <v>15876300</v>
       </c>
       <c r="E49" s="3">
-        <v>16179400</v>
+        <v>16591500</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
@@ -2013,10 +2013,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2808700</v>
+        <v>2880300</v>
       </c>
       <c r="E52" s="3">
-        <v>3182400</v>
+        <v>3263400</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -2079,10 +2079,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>41029400</v>
+        <v>42074400</v>
       </c>
       <c r="E54" s="3">
-        <v>40259100</v>
+        <v>41284400</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>3</v>
@@ -2142,10 +2142,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3071100</v>
+        <v>3149300</v>
       </c>
       <c r="E57" s="3">
-        <v>2431300</v>
+        <v>2493200</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -2175,10 +2175,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1057000</v>
+        <v>1083900</v>
       </c>
       <c r="E58" s="3">
-        <v>376200</v>
+        <v>385800</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -2208,10 +2208,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9874800</v>
+        <v>10126200</v>
       </c>
       <c r="E59" s="3">
-        <v>9791600</v>
+        <v>10041000</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
@@ -2241,10 +2241,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>14002800</v>
+        <v>14359400</v>
       </c>
       <c r="E60" s="3">
-        <v>12599000</v>
+        <v>12919900</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>3</v>
@@ -2274,10 +2274,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7300200</v>
+        <v>7486100</v>
       </c>
       <c r="E61" s="3">
-        <v>8399400</v>
+        <v>8613300</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2307,10 +2307,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6005200</v>
+        <v>6158200</v>
       </c>
       <c r="E62" s="3">
-        <v>4673100</v>
+        <v>4792200</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2439,10 +2439,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>27518000</v>
+        <v>28218900</v>
       </c>
       <c r="E66" s="3">
-        <v>25908300</v>
+        <v>26568100</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
@@ -2619,10 +2619,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>9753200</v>
+        <v>10001600</v>
       </c>
       <c r="E72" s="3">
-        <v>9890100</v>
+        <v>10142000</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -2751,10 +2751,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13511400</v>
+        <v>13855500</v>
       </c>
       <c r="E76" s="3">
-        <v>14350800</v>
+        <v>14716300</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
@@ -2855,10 +2855,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2376200</v>
+        <v>2436800</v>
       </c>
       <c r="E81" s="3">
-        <v>2035900</v>
+        <v>2087700</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>3</v>
@@ -2903,10 +2903,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1007100</v>
+        <v>1032700</v>
       </c>
       <c r="E83" s="3">
-        <v>981500</v>
+        <v>1006500</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -3101,10 +3101,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4811300</v>
+        <v>4933900</v>
       </c>
       <c r="E89" s="3">
-        <v>3632800</v>
+        <v>3725300</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
@@ -3149,10 +3149,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1057000</v>
+        <v>-1083900</v>
       </c>
       <c r="E91" s="3">
-        <v>-766500</v>
+        <v>-786000</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
@@ -3248,10 +3248,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-692300</v>
+        <v>-709900</v>
       </c>
       <c r="E94" s="3">
-        <v>-540000</v>
+        <v>-553700</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -3296,10 +3296,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1096600</v>
+        <v>-1124600</v>
       </c>
       <c r="E96" s="3">
-        <v>-1026200</v>
+        <v>-1052400</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3428,10 +3428,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2799800</v>
+        <v>-2871100</v>
       </c>
       <c r="E100" s="3">
-        <v>-2985300</v>
+        <v>-3061400</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
@@ -3461,10 +3461,10 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-90900</v>
+        <v>-93200</v>
       </c>
       <c r="E101" s="3">
-        <v>135600</v>
+        <v>139100</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3494,10 +3494,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1228400</v>
+        <v>1259700</v>
       </c>
       <c r="E102" s="3">
-        <v>243100</v>
+        <v>249300</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/BAESY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BAESY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
   <si>
     <t>BAESY</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -687,20 +687,20 @@
       <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="F7" s="2">
+        <v>44561</v>
+      </c>
+      <c r="G7" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H7" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I7" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J7" s="2">
+        <v>43100</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -715,25 +715,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>30283000</v>
+        <v>29395700</v>
       </c>
       <c r="E8" s="3">
-        <v>27894700</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>25613600</v>
+      </c>
+      <c r="F8" s="3">
+        <v>26432600</v>
+      </c>
+      <c r="G8" s="3">
+        <v>26318900</v>
+      </c>
+      <c r="H8" s="3">
+        <v>24243400</v>
+      </c>
+      <c r="I8" s="3">
+        <v>21438700</v>
+      </c>
+      <c r="J8" s="3">
+        <v>23280400</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -748,25 +748,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>10294200</v>
+        <v>10168400</v>
       </c>
       <c r="E9" s="3">
-        <v>9269400</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>8669200</v>
+      </c>
+      <c r="F9" s="3">
+        <v>9550200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>9371400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>8611400</v>
+      </c>
+      <c r="I9" s="3">
+        <v>7549000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>8224600</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -781,25 +781,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>19988700</v>
+        <v>19227300</v>
       </c>
       <c r="E10" s="3">
-        <v>18625400</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>16944400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>16882400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>16947500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>15632100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>13889700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>15055800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -829,25 +829,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>359500</v>
+        <v>2934700</v>
       </c>
       <c r="E12" s="3">
-        <v>362200</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+        <v>2412200</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2712200</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2191300</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1999900</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1920700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2173400</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -895,25 +895,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-56400</v>
+        <v>-57300</v>
       </c>
       <c r="E14" s="3">
-        <v>-108900</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>-102400</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-461700</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-109200</v>
+      </c>
+      <c r="H14" s="3">
+        <v>39700</v>
+      </c>
+      <c r="I14" s="3">
+        <v>210300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>521700</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -928,25 +928,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1026100</v>
+        <v>996100</v>
       </c>
       <c r="E15" s="3">
-        <v>1002500</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>920500</v>
+      </c>
+      <c r="F15" s="3">
+        <v>949200</v>
+      </c>
+      <c r="G15" s="3">
+        <v>916100</v>
+      </c>
+      <c r="H15" s="3">
+        <v>810500</v>
+      </c>
+      <c r="I15" s="3">
+        <v>442300</v>
+      </c>
+      <c r="J15" s="3">
+        <v>466300</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -973,25 +973,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>26906700</v>
+        <v>26388400</v>
       </c>
       <c r="E17" s="3">
-        <v>24766500</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>23105000</v>
+      </c>
+      <c r="F17" s="3">
+        <v>23935700</v>
+      </c>
+      <c r="G17" s="3">
+        <v>23980100</v>
+      </c>
+      <c r="H17" s="3">
+        <v>22062100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>19492500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>21208400</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1006,25 +1006,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3376300</v>
+        <v>3007300</v>
       </c>
       <c r="E18" s="3">
-        <v>3128300</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>2508600</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2496900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2338800</v>
+      </c>
+      <c r="H18" s="3">
+        <v>2181300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1946200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>2072000</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1054,25 +1054,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>120700</v>
+        <v>-163000</v>
       </c>
       <c r="E20" s="3">
-        <v>-165300</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>-67500</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-182800</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-287400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-140600</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1087,25 +1087,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4529800</v>
+        <v>4166500</v>
       </c>
       <c r="E21" s="3">
-        <v>3969500</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>3496600</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3628900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>3290400</v>
+      </c>
+      <c r="H21" s="3">
+        <v>3279300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2439400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2678900</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1120,25 +1120,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>444800</v>
+        <v>431800</v>
       </c>
       <c r="E22" s="3">
-        <v>353000</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>324100</v>
+      </c>
+      <c r="F22" s="3">
+        <v>337200</v>
+      </c>
+      <c r="G22" s="3">
+        <v>327700</v>
+      </c>
+      <c r="H22" s="3">
+        <v>311200</v>
+      </c>
+      <c r="I22" s="3">
+        <v>260000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>273000</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1153,25 +1153,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3052200</v>
+        <v>2962800</v>
       </c>
       <c r="E23" s="3">
-        <v>2610000</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>2396500</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2857100</v>
+      </c>
+      <c r="G23" s="3">
+        <v>2179000</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2153500</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1560000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1450300</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1186,25 +1186,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>506500</v>
+        <v>491700</v>
       </c>
       <c r="E24" s="3">
-        <v>413300</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>379500</v>
+      </c>
+      <c r="F24" s="3">
+        <v>268100</v>
+      </c>
+      <c r="G24" s="3">
+        <v>307200</v>
+      </c>
+      <c r="H24" s="3">
+        <v>124500</v>
+      </c>
+      <c r="I24" s="3">
+        <v>243400</v>
+      </c>
+      <c r="J24" s="3">
+        <v>292000</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1252,25 +1252,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2545700</v>
+        <v>2471100</v>
       </c>
       <c r="E26" s="3">
-        <v>2196600</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>2017000</v>
+      </c>
+      <c r="F26" s="3">
+        <v>2589000</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1871800</v>
+      </c>
+      <c r="H26" s="3">
+        <v>2029000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1316600</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1158300</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1285,25 +1285,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2436800</v>
+        <v>2365400</v>
       </c>
       <c r="E27" s="3">
-        <v>2087700</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>1917000</v>
+      </c>
+      <c r="F27" s="3">
+        <v>2380400</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1773500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1954800</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1274500</v>
+      </c>
+      <c r="J27" s="3">
+        <v>1117800</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1450,25 +1450,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-120700</v>
+        <v>163000</v>
       </c>
       <c r="E32" s="3">
-        <v>165300</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>67500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>182800</v>
+      </c>
+      <c r="G32" s="3">
+        <v>35500</v>
+      </c>
+      <c r="H32" s="3">
+        <v>287400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>51000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>140600</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1483,25 +1483,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2436800</v>
+        <v>2365400</v>
       </c>
       <c r="E33" s="3">
-        <v>2087700</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>1917000</v>
+      </c>
+      <c r="F33" s="3">
+        <v>2380400</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1773500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1954800</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1274500</v>
+      </c>
+      <c r="J33" s="3">
+        <v>1117800</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1549,25 +1549,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2436800</v>
+        <v>2365400</v>
       </c>
       <c r="E35" s="3">
-        <v>2087700</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>1917000</v>
+      </c>
+      <c r="F35" s="3">
+        <v>2380400</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1773500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1954800</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1274500</v>
+      </c>
+      <c r="J35" s="3">
+        <v>1117800</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1592,20 +1592,20 @@
       <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="F38" s="2">
+        <v>44561</v>
+      </c>
+      <c r="G38" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H38" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I38" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J38" s="2">
+        <v>43100</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1650,25 +1650,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2463000</v>
+        <v>5180400</v>
       </c>
       <c r="E41" s="3">
-        <v>2142800</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>3743600</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3949800</v>
+      </c>
+      <c r="G41" s="3">
+        <v>3779100</v>
+      </c>
+      <c r="H41" s="3">
+        <v>3426300</v>
+      </c>
+      <c r="I41" s="3">
+        <v>4119200</v>
+      </c>
+      <c r="J41" s="3">
+        <v>4421200</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1683,25 +1683,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3142700</v>
+        <v>54800</v>
       </c>
       <c r="E42" s="3">
-        <v>2264900</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>27700</v>
+      </c>
+      <c r="F42" s="3">
+        <v>10800</v>
+      </c>
+      <c r="G42" s="3">
+        <v>12300</v>
+      </c>
+      <c r="H42" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I42" s="3">
+        <v>110900</v>
+      </c>
+      <c r="J42" s="3">
+        <v>16200</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1716,25 +1716,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7101600</v>
+        <v>6840100</v>
       </c>
       <c r="E43" s="3">
-        <v>7597600</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>6929300</v>
+      </c>
+      <c r="F43" s="3">
+        <v>6028300</v>
+      </c>
+      <c r="G43" s="3">
+        <v>6623100</v>
+      </c>
+      <c r="H43" s="3">
+        <v>6121400</v>
+      </c>
+      <c r="I43" s="3">
+        <v>5395000</v>
+      </c>
+      <c r="J43" s="3">
+        <v>4811800</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1749,25 +1749,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1516900</v>
+        <v>1472500</v>
       </c>
       <c r="E44" s="3">
-        <v>1280700</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>1176000</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1098100</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1171400</v>
+      </c>
+      <c r="H44" s="3">
+        <v>1105900</v>
+      </c>
+      <c r="I44" s="3">
+        <v>986500</v>
+      </c>
+      <c r="J44" s="3">
+        <v>990700</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1782,25 +1782,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1224300</v>
+        <v>259800</v>
       </c>
       <c r="E45" s="3">
-        <v>667900</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>322900</v>
+      </c>
+      <c r="F45" s="3">
+        <v>251900</v>
+      </c>
+      <c r="G45" s="3">
+        <v>374100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>447700</v>
+      </c>
+      <c r="I45" s="3">
+        <v>286800</v>
+      </c>
+      <c r="J45" s="3">
+        <v>139200</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1815,25 +1815,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>15448500</v>
+        <v>14995900</v>
       </c>
       <c r="E46" s="3">
-        <v>13953900</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>12812800</v>
+      </c>
+      <c r="F46" s="3">
+        <v>11940100</v>
+      </c>
+      <c r="G46" s="3">
+        <v>12842000</v>
+      </c>
+      <c r="H46" s="3">
+        <v>12242900</v>
+      </c>
+      <c r="I46" s="3">
+        <v>12204800</v>
+      </c>
+      <c r="J46" s="3">
+        <v>11330700</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1848,25 +1848,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1304300</v>
+        <v>1294100</v>
       </c>
       <c r="E47" s="3">
-        <v>1278100</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>1244700</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1007400</v>
+      </c>
+      <c r="G47" s="3">
+        <v>745500</v>
+      </c>
+      <c r="H47" s="3">
+        <v>739000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>716300</v>
+      </c>
+      <c r="J47" s="3">
+        <v>550100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1881,25 +1881,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6564900</v>
+        <v>6300000</v>
       </c>
       <c r="E48" s="3">
-        <v>6197500</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>5614800</v>
+      </c>
+      <c r="F48" s="3">
+        <v>5339100</v>
+      </c>
+      <c r="G48" s="3">
+        <v>5062500</v>
+      </c>
+      <c r="H48" s="3">
+        <v>4734800</v>
+      </c>
+      <c r="I48" s="3">
+        <v>3014200</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3014100</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1914,25 +1914,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>15876300</v>
+        <v>15343700</v>
       </c>
       <c r="E49" s="3">
-        <v>16591500</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>15174400</v>
+      </c>
+      <c r="F49" s="3">
+        <v>15814100</v>
+      </c>
+      <c r="G49" s="3">
+        <v>15986300</v>
+      </c>
+      <c r="H49" s="3">
+        <v>13690500</v>
+      </c>
+      <c r="I49" s="3">
+        <v>13543000</v>
+      </c>
+      <c r="J49" s="3">
+        <v>13989300</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2013,25 +2013,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2880300</v>
+        <v>2022700</v>
       </c>
       <c r="E52" s="3">
-        <v>3263400</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>2541100</v>
+      </c>
+      <c r="F52" s="3">
+        <v>1676300</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1478600</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1410500</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1125400</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1266500</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2079,25 +2079,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>42074400</v>
+        <v>40841700</v>
       </c>
       <c r="E54" s="3">
-        <v>41284400</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>37908300</v>
+      </c>
+      <c r="F54" s="3">
+        <v>36742400</v>
+      </c>
+      <c r="G54" s="3">
+        <v>37586700</v>
+      </c>
+      <c r="H54" s="3">
+        <v>33944800</v>
+      </c>
+      <c r="I54" s="3">
+        <v>31539200</v>
+      </c>
+      <c r="J54" s="3">
+        <v>31137400</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2142,25 +2142,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3149300</v>
+        <v>3057000</v>
       </c>
       <c r="E57" s="3">
-        <v>2493200</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>2289300</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2193600</v>
+      </c>
+      <c r="G57" s="3">
+        <v>951600</v>
+      </c>
+      <c r="H57" s="3">
+        <v>894000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>896000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>805600</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2175,25 +2175,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1083900</v>
+        <v>1193500</v>
       </c>
       <c r="E58" s="3">
-        <v>385800</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>449400</v>
+      </c>
+      <c r="F58" s="3">
+        <v>950500</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1021200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>891300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>1014500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>94600</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2208,25 +2208,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10126200</v>
+        <v>6229900</v>
       </c>
       <c r="E59" s="3">
-        <v>10041000</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>5758200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>5035700</v>
+      </c>
+      <c r="G59" s="3">
+        <v>7200600</v>
+      </c>
+      <c r="H59" s="3">
+        <v>7374300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>6952500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>6341800</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2241,25 +2241,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>14359400</v>
+        <v>13938700</v>
       </c>
       <c r="E60" s="3">
-        <v>12919900</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>11863400</v>
+      </c>
+      <c r="F60" s="3">
+        <v>11774900</v>
+      </c>
+      <c r="G60" s="3">
+        <v>12810600</v>
+      </c>
+      <c r="H60" s="3">
+        <v>12095900</v>
+      </c>
+      <c r="I60" s="3">
+        <v>11833900</v>
+      </c>
+      <c r="J60" s="3">
+        <v>10264200</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2274,25 +2274,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7486100</v>
+        <v>7339400</v>
       </c>
       <c r="E61" s="3">
-        <v>8613300</v>
+        <v>7951100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>7876600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>8414300</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>5485700</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>4490100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>5525400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2307,25 +2307,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6158200</v>
+        <v>1212600</v>
       </c>
       <c r="E62" s="3">
-        <v>4792200</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>1216900</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1276900</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1309300</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1356200</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1813600</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1986900</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2439,25 +2439,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>28218900</v>
+        <v>27183200</v>
       </c>
       <c r="E66" s="3">
-        <v>26568100</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>24172500</v>
+      </c>
+      <c r="F66" s="3">
+        <v>26359500</v>
+      </c>
+      <c r="G66" s="3">
+        <v>30868100</v>
+      </c>
+      <c r="H66" s="3">
+        <v>26645900</v>
+      </c>
+      <c r="I66" s="3">
+        <v>24379000</v>
+      </c>
+      <c r="J66" s="3">
+        <v>24710400</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2619,25 +2619,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>10001600</v>
+        <v>3851800</v>
       </c>
       <c r="E72" s="3">
-        <v>10142000</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>3773700</v>
+      </c>
+      <c r="F72" s="3">
+        <v>560600</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-3295800</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-2493900</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-2637000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-3395300</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2751,25 +2751,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13855500</v>
+        <v>13449600</v>
       </c>
       <c r="E76" s="3">
-        <v>14716300</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>13512900</v>
+      </c>
+      <c r="F76" s="3">
+        <v>10068800</v>
+      </c>
+      <c r="G76" s="3">
+        <v>6339100</v>
+      </c>
+      <c r="H76" s="3">
+        <v>7161100</v>
+      </c>
+      <c r="I76" s="3">
+        <v>7068500</v>
+      </c>
+      <c r="J76" s="3">
+        <v>6368900</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2827,20 +2827,20 @@
       <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="F80" s="2">
+        <v>44561</v>
+      </c>
+      <c r="G80" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H80" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I80" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J80" s="2">
+        <v>43100</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2855,25 +2855,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2436800</v>
+        <v>2365400</v>
       </c>
       <c r="E81" s="3">
-        <v>2087700</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>1917000</v>
+      </c>
+      <c r="F81" s="3">
+        <v>2380400</v>
+      </c>
+      <c r="G81" s="3">
+        <v>1773500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>1954800</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1274500</v>
+      </c>
+      <c r="J81" s="3">
+        <v>1117800</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2903,25 +2903,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1032700</v>
+        <v>718400</v>
       </c>
       <c r="E83" s="3">
-        <v>1006500</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>661500</v>
+      </c>
+      <c r="F83" s="3">
+        <v>694600</v>
+      </c>
+      <c r="G83" s="3">
+        <v>741400</v>
+      </c>
+      <c r="H83" s="3">
+        <v>676800</v>
+      </c>
+      <c r="I83" s="3">
+        <v>342800</v>
+      </c>
+      <c r="J83" s="3">
+        <v>355500</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3101,25 +3101,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4933900</v>
+        <v>4789300</v>
       </c>
       <c r="E89" s="3">
-        <v>3725300</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>3420700</v>
+      </c>
+      <c r="F89" s="3">
+        <v>3313400</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1591900</v>
+      </c>
+      <c r="H89" s="3">
+        <v>2115100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>1529400</v>
+      </c>
+      <c r="J89" s="3">
+        <v>2564000</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3149,25 +3149,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1083900</v>
+        <v>-1052100</v>
       </c>
       <c r="E91" s="3">
-        <v>-786000</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+        <v>-721700</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-698700</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-525600</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-476800</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-456300</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-525800</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3248,25 +3248,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-709900</v>
+        <v>-689100</v>
       </c>
       <c r="E94" s="3">
-        <v>-553700</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-508500</v>
+      </c>
+      <c r="F94" s="3">
+        <v>89400</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-2781100</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-307300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-456300</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-486600</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3296,25 +3296,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1124600</v>
+        <v>1091600</v>
       </c>
       <c r="E96" s="3">
-        <v>-1052400</v>
+        <v>966300</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>1052100</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>1018500</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>958900</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>896000</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>924500</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3428,25 +3428,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2871100</v>
+        <v>-2787000</v>
       </c>
       <c r="E100" s="3">
-        <v>-3061400</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>-2811000</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-3054800</v>
+      </c>
+      <c r="G100" s="3">
+        <v>1328400</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-2598500</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-1166200</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-1344900</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3461,25 +3461,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-93200</v>
+        <v>-90400</v>
       </c>
       <c r="E101" s="3">
-        <v>139100</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>127700</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-63600</v>
+      </c>
+      <c r="I101" s="3">
+        <v>52300</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-66200</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3494,25 +3494,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1259700</v>
+        <v>1222800</v>
       </c>
       <c r="E102" s="3">
-        <v>249300</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>228900</v>
+      </c>
+      <c r="F102" s="3">
+        <v>338500</v>
+      </c>
+      <c r="G102" s="3">
+        <v>109200</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-854200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>666400</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/BAESY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BAESY_YR_FIN.xlsx
@@ -656,160 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>32940600</v>
+      </c>
+      <c r="E8" s="3">
         <v>29395700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25613600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26432600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>26318900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24243400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21438700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23280400</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>10168400</v>
+        <v>28692900</v>
       </c>
       <c r="E9" s="3">
-        <v>8669200</v>
+        <v>25614000</v>
       </c>
       <c r="F9" s="3">
-        <v>9550200</v>
+        <v>22271200</v>
       </c>
       <c r="G9" s="3">
-        <v>9371400</v>
+        <v>23043400</v>
       </c>
       <c r="H9" s="3">
-        <v>8611400</v>
+        <v>23181400</v>
       </c>
       <c r="I9" s="3">
-        <v>7549000</v>
+        <v>21256900</v>
       </c>
       <c r="J9" s="3">
+        <v>18730300</v>
+      </c>
+      <c r="K9" s="3">
         <v>8224600</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>19227300</v>
+        <v>4247800</v>
       </c>
       <c r="E10" s="3">
-        <v>16944400</v>
+        <v>3781800</v>
       </c>
       <c r="F10" s="3">
-        <v>16882400</v>
+        <v>3342400</v>
       </c>
       <c r="G10" s="3">
-        <v>16947500</v>
+        <v>3389200</v>
       </c>
       <c r="H10" s="3">
-        <v>15632100</v>
+        <v>3137500</v>
       </c>
       <c r="I10" s="3">
-        <v>13889700</v>
+        <v>2986600</v>
       </c>
       <c r="J10" s="3">
+        <v>2708400</v>
+      </c>
+      <c r="K10" s="3">
         <v>15055800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,41 +835,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2381200</v>
+      </c>
+      <c r="E12" s="3">
         <v>2934700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2412200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2712200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2191300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1999900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1920700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2173400</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,75 +904,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-57300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-102400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-461700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-109200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>39700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>210300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>521700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1358300</v>
+      </c>
+      <c r="E15" s="3">
         <v>996100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>920500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>949200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>916100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>810500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>442300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>466300</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +992,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29844600</v>
+      </c>
+      <c r="E17" s="3">
         <v>26388400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23105000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23935700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23980100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>22062100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19492500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21208400</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3096000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3007300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2508600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2496900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2338800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2181300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1946200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2072000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,173 +1080,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-350500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-163000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-67500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-182800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-35500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-287400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-51000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-140600</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4804900</v>
+      </c>
+      <c r="E21" s="3">
         <v>4166500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3496600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3628900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3290400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3279300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2439400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2678900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>694800</v>
+      </c>
+      <c r="E22" s="3">
         <v>431800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>324100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>337200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>327700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>311200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>260000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>273000</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2919500</v>
+      </c>
+      <c r="E23" s="3">
         <v>2962800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2396500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2857100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2179000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2153500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1560000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1450300</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>364300</v>
+      </c>
+      <c r="E24" s="3">
         <v>491700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>379500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>268100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>307200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>124500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>243400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>292000</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1293,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2555200</v>
+      </c>
+      <c r="E26" s="3">
         <v>2471100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2017000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2589000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1871800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2029000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1316600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1158300</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2448800</v>
+      </c>
+      <c r="E27" s="3">
         <v>2365400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1917000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2380400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1773500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1954800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1274500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1117800</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1374,12 +1434,15 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,75 +1509,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>350500</v>
+      </c>
+      <c r="E32" s="3">
         <v>163000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>67500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>182800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>35500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>287400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>51000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>140600</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2448800</v>
+      </c>
+      <c r="E33" s="3">
         <v>2365400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1917000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2380400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1773500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1954800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1274500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1117800</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1617,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2448800</v>
+      </c>
+      <c r="E35" s="3">
         <v>2365400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1917000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2380400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1773500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1954800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1274500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1117800</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,305 +1729,333 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4229000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5180400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3743600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3949800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3779100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3426300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4119200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4421200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E42" s="3">
         <v>54800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>27700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>110900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>16200</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7241100</v>
+      </c>
+      <c r="E43" s="3">
         <v>6840100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6929300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6028300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6623100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6121400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5395000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4811800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1657500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1472500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1176000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1098100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1171400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1105900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>986500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>990700</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>266700</v>
+      </c>
+      <c r="E45" s="3">
         <v>259800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>322900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>251900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>374100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>447700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>286800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>139200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14713900</v>
+      </c>
+      <c r="E46" s="3">
         <v>14995900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12812800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11940100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12842000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12242900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12204800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11330700</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1062900</v>
+      </c>
+      <c r="E47" s="3">
         <v>1294100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1244700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1007400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>745500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>739000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>716300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>550100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8260200</v>
+      </c>
+      <c r="E48" s="3">
         <v>6300000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5614800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5339100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5062500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4734800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3014200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3014100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20284900</v>
+      </c>
+      <c r="E49" s="3">
         <v>15343700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15174400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15814100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15986300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13690500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13543000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13989300</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,42 +2122,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2803100</v>
+      </c>
+      <c r="E52" s="3">
         <v>2022700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2541100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1676300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1478600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1410500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1125400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1266500</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2194,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>47750900</v>
+      </c>
+      <c r="E54" s="3">
         <v>40841700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37908300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36742400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37586700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33944800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>31539200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31137400</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,206 +2265,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3857200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3057000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2289300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2193600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>951600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>894000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>896000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>805600</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1153000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1193500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>449400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>950500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1021200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>891300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1014500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>94600</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6737900</v>
+      </c>
+      <c r="E59" s="3">
         <v>6229900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5758200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5035700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7200600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7374300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6952500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6341800</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15451300</v>
+      </c>
+      <c r="E60" s="3">
         <v>13938700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11863400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11774900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12810600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12095900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11833900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10264200</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11761800</v>
+      </c>
+      <c r="E61" s="3">
         <v>7339400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7951100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7876600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8414300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5485700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4490100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5525400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1382100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1212600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1216900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1276900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1309300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1356200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1813600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1986900</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2586,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33007000</v>
+      </c>
+      <c r="E66" s="3">
         <v>27183200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24172500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26359500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>30868100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26645900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24379000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24710400</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2782,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5055300</v>
+      </c>
+      <c r="E72" s="3">
         <v>3851800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3773700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>560600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3295800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2493900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2637000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3395300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2926,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14542400</v>
+      </c>
+      <c r="E76" s="3">
         <v>13449600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13512900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10068800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6339100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7161100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7068500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6368900</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +2998,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2448800</v>
+      </c>
+      <c r="E81" s="3">
         <v>2365400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1917000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2380400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1773500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1954800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1274500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1117800</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3094,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>830000</v>
+      </c>
+      <c r="E83" s="3">
         <v>718400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>661500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>694600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>741400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>676800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>342800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>355500</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3307,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4913800</v>
+      </c>
+      <c r="E89" s="3">
         <v>4789300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3420700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3313400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1591900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2115100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1529400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2564000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3362,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1239400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1052100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-721700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-698700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-525600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-476800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-456300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-525800</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3467,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6596400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-689100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-508500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>89400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2781100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-307300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-456300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-486600</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,41 +3522,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1173100</v>
+      </c>
+      <c r="E96" s="3">
         <v>1091600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>966300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1052100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1018500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>958900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>896000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>924500</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,106 +3663,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>870100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2787000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2811000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3054800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1328400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2598500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1166200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1344900</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-50100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-90400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>127700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-30000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-63600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>52300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-66200</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-862600</v>
+      </c>
+      <c r="E102" s="3">
         <v>1222800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>228900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>338500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>109200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-854200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-40800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>666400</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BAESY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BAESY_YR_FIN.xlsx
@@ -656,172 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>38137300</v>
+      </c>
+      <c r="E8" s="3">
         <v>32940600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>29395700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>25613600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>26432600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>26318900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24243400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21438700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>23280400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>28692900</v>
+        <v>33098300</v>
       </c>
       <c r="E9" s="3">
-        <v>25614000</v>
+        <v>28651600</v>
       </c>
       <c r="F9" s="3">
+        <v>25575700</v>
+      </c>
+      <c r="G9" s="3">
         <v>22271200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>23043400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>23181400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>21256900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18730300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8224600</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>4247800</v>
+        <v>5039000</v>
       </c>
       <c r="E10" s="3">
-        <v>3781800</v>
+        <v>4289100</v>
       </c>
       <c r="F10" s="3">
+        <v>3820000</v>
+      </c>
+      <c r="G10" s="3">
         <v>3342400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3389200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3137500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2986600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2708400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15055800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,44 +848,48 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>2381200</v>
+        <v>4310900</v>
       </c>
       <c r="E12" s="3">
+        <v>3382700</v>
+      </c>
+      <c r="F12" s="3">
         <v>2934700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2412200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2712200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2191300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1999900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1920700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2173400</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,81 +923,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-21300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-57300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-102400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-461700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-109200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>39700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>210300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>521700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1561200</v>
+      </c>
+      <c r="E15" s="3">
         <v>1358300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>996100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>920500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>949200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>916100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>810500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>442300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>466300</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,80 +1018,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34436100</v>
+      </c>
+      <c r="E17" s="3">
         <v>29844600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>26388400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23105000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23935700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23980100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>22062100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19492500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21208400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3701200</v>
+      </c>
+      <c r="E18" s="3">
         <v>3096000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3007300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2508600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2496900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2338800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2181300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1946200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2072000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,188 +1113,204 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-282600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-350500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-163000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-67500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-182800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-35500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-287400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-51000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-140600</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5545100</v>
+      </c>
+      <c r="E21" s="3">
         <v>4804900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4166500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3496600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3628900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3290400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3279300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2439400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2678900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>678300</v>
+      </c>
+      <c r="E22" s="3">
         <v>694800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>431800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>324100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>337200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>327700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>311200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>260000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>273000</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3461600</v>
+      </c>
+      <c r="E23" s="3">
         <v>2919500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2962800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2396500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2857100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2179000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2153500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1560000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1450300</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>566600</v>
+      </c>
+      <c r="E24" s="3">
         <v>364300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>491700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>379500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>268100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>307200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>124500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>243400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>292000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,81 +1344,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2895000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2555200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2471100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2017000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2589000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1871800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2029000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1316600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1158300</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2775200</v>
+      </c>
+      <c r="E27" s="3">
         <v>2448800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2365400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1917000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2380400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1773500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1954800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1274500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1117800</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,9 +1461,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1437,12 +1497,15 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,81 +1578,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>282600</v>
+      </c>
+      <c r="E32" s="3">
         <v>350500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>163000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>67500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>182800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>35500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>287400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>51000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>140600</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2775200</v>
+      </c>
+      <c r="E33" s="3">
         <v>2448800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2365400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1917000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2380400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1773500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1954800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1274500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1117800</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,86 +1695,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2775200</v>
+      </c>
+      <c r="E35" s="3">
         <v>2448800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2365400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1917000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2380400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1773500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1954800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1274500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1117800</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,332 +1815,360 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4627200</v>
+      </c>
+      <c r="E41" s="3">
         <v>4229000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5180400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3743600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3949800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3779100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3426300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4119200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4421200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E42" s="3">
         <v>61300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>54800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>27700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>110900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>16200</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8300100</v>
+      </c>
+      <c r="E43" s="3">
         <v>7241100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6840100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6929300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6028300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6623100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6121400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5395000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4811800</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1862700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1657500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1472500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1176000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1098100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1171400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1105900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>986500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>990700</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>273200</v>
+      </c>
+      <c r="E45" s="3">
         <v>266700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>259800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>322900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>251900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>374100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>447700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>286800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>139200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16348600</v>
+      </c>
+      <c r="E46" s="3">
         <v>14713900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14995900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12812800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11940100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12842000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12242900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12204800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11330700</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1062900</v>
+        <v>1214000</v>
       </c>
       <c r="E47" s="3">
+        <v>1272000</v>
+      </c>
+      <c r="F47" s="3">
         <v>1294100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1244700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1007400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>745500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>739000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>716300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>550100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9149400</v>
+      </c>
+      <c r="E48" s="3">
         <v>8260200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6300000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5614800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5339100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5062500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4734800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3014200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3014100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20417200</v>
+      </c>
+      <c r="E49" s="3">
         <v>20284900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15343700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15174400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15814100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15986300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13690500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13543000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13989300</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,45 +2241,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2803100</v>
+        <v>3071300</v>
       </c>
       <c r="E52" s="3">
+        <v>2594000</v>
+      </c>
+      <c r="F52" s="3">
         <v>2022700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2541100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1676300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1478600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1410500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1125400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1266500</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,45 +2319,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>50712000</v>
+      </c>
+      <c r="E54" s="3">
         <v>47750900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>40841700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37908300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36742400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>37586700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33944800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31539200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>31137400</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,224 +2395,243 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4506100</v>
+      </c>
+      <c r="E57" s="3">
         <v>3857200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3057000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2289300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2193600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>951600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>894000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>896000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>805600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>508700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1153000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1193500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>449400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>950500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1021200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>891300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1014500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>94600</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7554500</v>
+      </c>
+      <c r="E59" s="3">
         <v>6737900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6229900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5758200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5035700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7200600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7374300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6952500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6341800</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16558500</v>
+      </c>
+      <c r="E60" s="3">
         <v>15451300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13938700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11863400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11774900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12810600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12095900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11833900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10264200</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11818300</v>
+      </c>
+      <c r="E61" s="3">
         <v>11761800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7339400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7951100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7876600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8414300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5485700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4490100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5525400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1481800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1382100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1212600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1216900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1276900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1309300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1356200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1813600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1986900</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,45 +2743,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34646000</v>
+      </c>
+      <c r="E66" s="3">
         <v>33007000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27183200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24172500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26359500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>30868100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26645900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24379000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24710400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2749,9 +2916,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,45 +2955,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6424000</v>
+      </c>
+      <c r="E72" s="3">
         <v>5055300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3851800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3773700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>560600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3295800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2493900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2637000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3395300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,45 +3111,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15860000</v>
+      </c>
+      <c r="E76" s="3">
         <v>14542400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13449600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13512900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10068800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6339100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7161100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7068500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6368900</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,86 +3189,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2775200</v>
+      </c>
+      <c r="E81" s="3">
         <v>2448800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2365400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1917000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2380400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1773500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1954800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1274500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1117800</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,44 +3292,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>924600</v>
+      </c>
+      <c r="E83" s="3">
         <v>830000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>718400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>661500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>694600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>741400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>676800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>342800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>355500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,45 +3523,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4619100</v>
+      </c>
+      <c r="E89" s="3">
         <v>4913800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4789300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3420700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3313400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1591900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2115100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1529400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2564000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,44 +3582,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1238200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1239400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1052100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-721700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-698700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-525600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-476800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-456300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-525800</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,45 +3696,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-728100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6596400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-689100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-508500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>89400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2781100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-307300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-456300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-486600</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,44 +3755,48 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1382200</v>
+      </c>
+      <c r="E96" s="3">
         <v>1173100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1091600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>966300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1052100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1018500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>958900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>896000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>924500</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,115 +3908,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3733500</v>
+      </c>
+      <c r="E100" s="3">
         <v>870100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2787000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2811000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3054800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1328400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2598500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1166200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1344900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-76700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-50100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-90400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>127700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-30000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-63600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>52300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-66200</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-862600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1222800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>228900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>338500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>109200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-854200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-40800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>666400</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
